--- a/output/pdf_financials_xlsx/GGM.xlsx
+++ b/output/pdf_financials_xlsx/GGM.xlsx
@@ -1262,19 +1262,19 @@
         <v>5.533878</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>6.133942</v>
+        <v>-0.133836</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>6.595252</v>
+        <v>0.467272</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2.062284</v>
+        <v>-2.062284</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.225495</v>
+        <v>-0.225495</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>4.564278</v>
+        <v>-4.564278</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-3.70371</v>
@@ -1289,10 +1289,10 @@
         <v>-2.878299</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.92973</v>
+        <v>-1.92973</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1.82277</v>
+        <v>-1.82277</v>
       </c>
     </row>
     <row r="17">
@@ -1310,10 +1310,10 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-21.768564</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.242492</v>
+        <v>-5.517058</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-5.483862</v>
@@ -1543,28 +1543,28 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>10.884282</v>
+        <v>-10.884282</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.637283</v>
+        <v>-2.637283</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5.510025</v>
+        <v>-5.510025</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.133889</v>
+        <v>-3.133889</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.06399</v>
+        <v>-3.06399</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.062284</v>
+        <v>-2.062284</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.225495</v>
+        <v>-0.225495</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>4.564278</v>
+        <v>-4.564278</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-3.70371</v>
@@ -1579,10 +1579,10 @@
         <v>-2.878299</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.92973</v>
+        <v>-1.92973</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>1.82277</v>
+        <v>-1.82277</v>
       </c>
     </row>
     <row r="21">
@@ -1716,28 +1716,28 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>10.884282</v>
+        <v>-10.884282</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.637283</v>
+        <v>-2.637283</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.510025</v>
+        <v>-5.510025</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.133889</v>
+        <v>-3.133889</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.06399</v>
+        <v>-3.06399</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.062284</v>
+        <v>-2.062284</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.225495</v>
+        <v>-0.225495</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4.564278</v>
+        <v>-4.564278</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-3.70371</v>
@@ -1752,10 +1752,10 @@
         <v>-2.878299</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.92973</v>
+        <v>-1.92973</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1.82277</v>
+        <v>-1.82277</v>
       </c>
     </row>
     <row r="24">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>181.4047</v>
+        <v>-181.4047</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>275.50125</v>
+        <v>-275.50125</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>51.5571</v>
+        <v>-51.5571</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>65.203971</v>
+        <v>-65.203971</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>80.515435</v>
@@ -1937,7 +1937,7 @@
         <v>151.489421</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>160.810833</v>
+        <v>-160.810833</v>
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
@@ -1971,19 +1971,19 @@
         <v>5.533878</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>6.133942</v>
+        <v>-0.133836</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.595252</v>
+        <v>0.467272</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2.062284</v>
+        <v>-2.062284</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.225495</v>
+        <v>-0.225495</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>4.564278</v>
+        <v>-4.564278</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-3.70371</v>
@@ -1998,10 +1998,10 @@
         <v>-2.878299</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.92973</v>
+        <v>-1.92973</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.82277</v>
+        <v>-1.82277</v>
       </c>
     </row>
     <row r="28">
@@ -2087,19 +2087,19 @@
         <v>5.559906</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>6.152704</v>
+        <v>-0.115074</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>6.60882</v>
+        <v>0.48084</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.086438</v>
+        <v>-2.03813</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.242682</v>
+        <v>-0.208308</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>4.602874</v>
+        <v>-4.525682</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-3.658686</v>
@@ -2114,10 +2114,10 @@
         <v>-2.836442</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.960047</v>
+        <v>-1.899413</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.838629</v>
+        <v>-1.806911</v>
       </c>
     </row>
     <row r="30">
@@ -2224,28 +2224,28 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>8.420518964155185</v>
+        <v>191.5794810358448</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>99.09618535139373</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>48.90905391671457</v>
+        <v>-2241.588959622224</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>53.54248783822059</v>
+        <v>755.7187248540464</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -2260,10 +2260,10 @@
         <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5741,43 +5741,43 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>8.238587000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.647749</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.224515</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.337947</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.237782</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.8988</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.667842</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.729725</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.240654</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.431427</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.59334</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.009177</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.598099</v>
       </c>
       <c r="Q92" s="3" t="n">
         <v>0</v>
@@ -6103,10 +6103,10 @@
         <v>-5.510025</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>3.133889</v>
+        <v>-3.133889</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>3.06399</v>
+        <v>-3.06399</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-2.062284</v>
@@ -11644,7 +11644,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -13060,7 +13064,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -14352,7 +14360,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -15372,7 +15384,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -16614,7 +16630,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -17092,7 +17112,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -18160,7 +18184,11 @@
           <t>Share-based payments reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -38018,10 +38046,10 @@
         </is>
       </c>
       <c r="S314" s="5" t="n">
-        <v>1.92973</v>
+        <v>-1.92973</v>
       </c>
       <c r="T314" s="5" t="n">
-        <v>1.82277</v>
+        <v>-1.82277</v>
       </c>
     </row>
     <row r="315">
@@ -47636,13 +47664,13 @@
         </is>
       </c>
       <c r="G420" s="5" t="n">
-        <v>10.884282</v>
+        <v>-10.884282</v>
       </c>
       <c r="H420" s="5" t="n">
-        <v>2.637283</v>
+        <v>-2.637283</v>
       </c>
       <c r="I420" s="5" t="n">
-        <v>5.510025</v>
+        <v>-5.510025</v>
       </c>
       <c r="J420" t="inlineStr">
         <is>
@@ -47655,16 +47683,16 @@
         </is>
       </c>
       <c r="L420" s="5" t="n">
-        <v>2.062284</v>
+        <v>-2.062284</v>
       </c>
       <c r="M420" s="5" t="n">
-        <v>0.225495</v>
+        <v>-0.225495</v>
       </c>
       <c r="N420" s="5" t="n">
-        <v>4.564278</v>
+        <v>-4.564278</v>
       </c>
       <c r="O420" s="5" t="n">
-        <v>3.70371</v>
+        <v>-3.70371</v>
       </c>
       <c r="P420" t="inlineStr">
         <is>
@@ -50039,13 +50067,13 @@
         </is>
       </c>
       <c r="J446" s="5" t="n">
-        <v>3.133889</v>
+        <v>-3.133889</v>
       </c>
       <c r="K446" s="5" t="n">
-        <v>3.06399</v>
+        <v>-3.06399</v>
       </c>
       <c r="L446" s="5" t="n">
-        <v>2.062284</v>
+        <v>-2.062284</v>
       </c>
       <c r="M446" t="inlineStr">
         <is>
@@ -52482,10 +52510,10 @@
         </is>
       </c>
       <c r="I472" s="5" t="n">
-        <v>5.510025</v>
+        <v>-5.510025</v>
       </c>
       <c r="J472" s="5" t="n">
-        <v>3.133899</v>
+        <v>-3.133899</v>
       </c>
       <c r="K472" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GGM.xlsx
+++ b/output/pdf_financials_xlsx/GGM.xlsx
@@ -945,10 +945,10 @@
         <v>0.026574</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.001975</v>
+        <v>1.218526</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.003303</v>
+        <v>1.069701</v>
       </c>
     </row>
     <row r="11">
@@ -1002,10 +1002,10 @@
         <v>-0.026574</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.001975</v>
+        <v>-1.218526</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.003303</v>
+        <v>-1.069701</v>
       </c>
     </row>
     <row r="12">
@@ -2381,22 +2381,22 @@
         <v>0.052449</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.152227</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.035157</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.05761</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.11961</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.080179</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.168267</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.267914</v>
@@ -2408,13 +2408,13 @@
         <v>0.132159</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.015407</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.009146</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.011013</v>
       </c>
     </row>
     <row r="35">
@@ -2495,22 +2495,22 @@
         <v>0.052449</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.152227</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.035157</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.05761</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.11961</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.080179</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.168267</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.267914</v>
@@ -2522,13 +2522,13 @@
         <v>0.47499</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.12092</v>
+        <v>0.136327</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.111811</v>
+        <v>0.120957</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.037367</v>
+        <v>0.04838</v>
       </c>
     </row>
     <row r="37">
@@ -3179,22 +3179,22 @@
         <v>0.400643</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.244226</v>
+        <v>0.091999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.08684699999999999</v>
+        <v>0.05169</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.05861</v>
+        <v>0.001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.157277</v>
+        <v>0.037667</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.081179</v>
+        <v>0.001</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.169267</v>
+        <v>0.001</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.001</v>
@@ -3206,13 +3206,13 @@
         <v>0.096488</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.019333</v>
+        <v>0.003926</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.018764</v>
+        <v>0.009618</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.036358</v>
+        <v>0.025345</v>
       </c>
     </row>
     <row r="49">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8936,7 +8936,11 @@
           <t>Reclamation deposit 7</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -10374,7 +10378,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -13458,7 +13462,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -37118,7 +37122,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">

--- a/output/pdf_financials_xlsx/GGM.xlsx
+++ b/output/pdf_financials_xlsx/GGM.xlsx
@@ -849,46 +849,46 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>1.110237</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>1.000091</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.317684</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.217095</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>0.10113</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>0.130875</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>0.258247</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>0.07557700000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>0.080359</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>0.130745</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>0.042001</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>0.013344</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>0.179235</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>0.004606</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>0</v>
@@ -906,43 +906,43 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>1.110237</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.996451</v>
+        <v>1.996542</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.123426</v>
+        <v>1.44111</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.554576</v>
+        <v>0.771671</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.715317</v>
+        <v>0.816447</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.713909</v>
+        <v>0.844784</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.204795</v>
+        <v>0.463042</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.10244</v>
+        <v>0.178017</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.121178</v>
+        <v>0.201537</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.068439</v>
+        <v>0.199184</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.039666</v>
+        <v>0.081667</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.057948</v>
+        <v>0.07129199999999999</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.026574</v>
+        <v>0.205809</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>1.218526</v>
@@ -963,43 +963,43 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.012229</v>
+        <v>-1.098008</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.996451</v>
+        <v>-1.996542</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-1.123426</v>
+        <v>-1.44111</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.554576</v>
+        <v>-0.771671</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.715317</v>
+        <v>-0.816447</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.713909</v>
+        <v>-0.844784</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.204795</v>
+        <v>-0.463042</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.10244</v>
+        <v>-0.178017</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.121178</v>
+        <v>-0.201537</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.068439</v>
+        <v>-0.199184</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.039666</v>
+        <v>-0.081667</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.057948</v>
+        <v>-0.07129199999999999</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.026574</v>
+        <v>-0.205809</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>-1.218526</v>
@@ -39012,7 +39012,11 @@
           <t>Personnel costs</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -43422,7 +43426,11 @@
           <t>Personnel costs</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -46350,7 +46358,11 @@
           <t>Personnel costs</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -50988,7 +51000,11 @@
           <t>Personnel costs</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
           <t>-</t>
@@ -54702,7 +54718,11 @@
           <t>Personnel costs a - 1,110,237</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GGM.xlsx
+++ b/output/pdf_financials_xlsx/GGM.xlsx
@@ -1313,7 +1313,7 @@
         <v>-21.768564</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-5.517058</v>
+        <v>0.242492</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-5.483862</v>
@@ -1549,10 +1549,10 @@
         <v>-2.637283</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-5.510025</v>
+        <v>-5.460009</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-3.133889</v>
+        <v>-2.989266</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-3.06399</v>
@@ -1606,10 +1606,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.050016</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>-0.144633</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
@@ -2227,7 +2227,7 @@
         <v>200</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>191.5794810358448</v>
+        <v>8.420518964155185</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>99.09618535139373</v>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.368371</v>
+        <v>5.338371</v>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
@@ -4125,10 +4125,10 @@
         <v>1.365639</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>1.49798</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>1.5503</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -4146,19 +4146,19 @@
         <v>0</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.862609</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.369843</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>1.044033</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>1.134585</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>1.453324</v>
       </c>
     </row>
     <row r="65">
@@ -4326,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.328053</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.825502</v>
       </c>
     </row>
     <row r="68">
@@ -4353,10 +4353,10 @@
         <v>1.365639</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>1.49798</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>1.5503</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0</v>
@@ -4374,19 +4374,19 @@
         <v>0</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>0.862609</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>0.369843</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>1.044033</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0</v>
+        <v>1.462638</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0</v>
+        <v>2.278826</v>
       </c>
     </row>
     <row r="69">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>3.751918</v>
+        <v>2.201618</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>3.999072</v>
@@ -4773,19 +4773,19 @@
         <v>6.263483</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>7.240808</v>
+        <v>6.378199</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>8.234957</v>
+        <v>7.865114</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>9.707426</v>
+        <v>8.663392999999999</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>11.324361</v>
+        <v>9.861723</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>12.271892</v>
+        <v>9.993066000000001</v>
       </c>
     </row>
     <row r="76">
@@ -6100,13 +6100,13 @@
         <v>-2.637283</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-5.510025</v>
+        <v>-5.460009</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-3.133889</v>
+        <v>-2.989266</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>-3.06399</v>
+        <v>-3.531262</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-2.062284</v>
@@ -6767,10 +6767,10 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.029296</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.014161</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
@@ -6817,22 +6817,22 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.047724</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.1317</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.050657</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.184144</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.036481</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -8226,22 +8226,22 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.047724</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.1317</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.050657</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.184144</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.036481</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -8285,22 +8285,22 @@
         <v>-2.51592</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-3.588011</v>
+        <v>-3.635735</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-2.836181</v>
+        <v>-2.967881</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-1.482354</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-2.102461</v>
+        <v>-2.153118</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-5.301839</v>
+        <v>-5.485983</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-1.823179</v>
+        <v>-1.85966</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-0.122752</v>
@@ -25258,7 +25258,11 @@
           <t>Purchase of equipment 9</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -26282,7 +26286,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -28870,7 +28878,11 @@
           <t>Purchase of equipment 9</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -30994,7 +31006,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -31182,7 +31198,11 @@
           <t>Issuance of common shares and warrants by private placement</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -32554,7 +32574,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -33486,7 +33510,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -51852,7 +51880,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr">
         <is>
           <t>-</t>
@@ -52316,7 +52348,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -52338,10 +52374,10 @@
         </is>
       </c>
       <c r="I470" s="5" t="n">
-        <v>5.460009</v>
+        <v>-5.460009</v>
       </c>
       <c r="J470" s="5" t="n">
-        <v>2.989266</v>
+        <v>-2.989266</v>
       </c>
       <c r="K470" t="inlineStr">
         <is>
@@ -52410,7 +52446,11 @@
           <t>Loss from discontinued operations (Note 9)</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -52432,10 +52472,10 @@
         </is>
       </c>
       <c r="I471" s="5" t="n">
-        <v>0.050016</v>
+        <v>-0.050016</v>
       </c>
       <c r="J471" s="5" t="n">
-        <v>0.144633</v>
+        <v>-0.144633</v>
       </c>
       <c r="K471" t="inlineStr">
         <is>
